--- a/ci-cd-merge-resolver/repoCollector/datasets/camunda.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/camunda.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -44,46 +44,31 @@
     <t>isMultiModule</t>
   </si>
   <si>
-    <t>4dcc386cd84a85861dc47fe13216e55deef1bad6</t>
-  </si>
-  <si>
-    <t>79ed19710d0d113cf60779ef2834627e55856481</t>
-  </si>
-  <si>
-    <t>9060494cce20393335d2e98abd816ca06f506ae8</t>
-  </si>
-  <si>
-    <t>82bce39ff892616b0cf881b4aacf58f16beccdd5</t>
-  </si>
-  <si>
-    <t>112c7986aa79d62547c8cab393cdc33bba730000</t>
-  </si>
-  <si>
-    <t>735f8fb00e6744fb98306f72f2ccf267f819bc3a</t>
-  </si>
-  <si>
-    <t>c97d33eef2c5239dce7a1f99a3f321759dbcbee0</t>
-  </si>
-  <si>
-    <t>0411de6f46bc50e48830002a429dc872ffc8e503</t>
-  </si>
-  <si>
-    <t>3909e2ce7585388ee919f250d0ed1baa916ba6bf</t>
-  </si>
-  <si>
-    <t>3a2ef37bf8e98defa4294514c20fd1a9bf36c2a6</t>
-  </si>
-  <si>
-    <t>12b1bc659433e79cc4d84194a826ee3af924a308</t>
-  </si>
-  <si>
-    <t>ca205d4cc7e431174b5375315d1e9a12cef7599e</t>
-  </si>
-  <si>
-    <t>771b9a6b37ec54ed48a5b494b53a6a02d1c170b2</t>
-  </si>
-  <si>
-    <t>bd52a5afdf32bd5412f49b754e6e6cf62c3c774c</t>
+    <t>70b043eb7fd7b4b6c21406cee7eb86debfb26694</t>
+  </si>
+  <si>
+    <t>dece32b1644ace90f90d43db99657863576e347d</t>
+  </si>
+  <si>
+    <t>1287a79b7d1e4d5a12bd55dee43020f4c9d89d27</t>
+  </si>
+  <si>
+    <t>2535e17b34852d87017bd2ccad5a4b26c027bc0a</t>
+  </si>
+  <si>
+    <t>d2e307aac44a0f8d17f2bba564c792df64a143c1</t>
+  </si>
+  <si>
+    <t>8a75e2505ddc80dea09069b152f3f36daf50ca6a</t>
+  </si>
+  <si>
+    <t>519eec426fff51239e1a234877c3150cd7386b89</t>
+  </si>
+  <si>
+    <t>fc98532cc277e1392f75fd927d5737fc28fd7853</t>
+  </si>
+  <si>
+    <t>d6185d0e3af065ac42936df85ed17c20c3e9f773</t>
   </si>
 </sst>
 </file>
@@ -128,7 +113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -174,7 +159,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>1984.0</v>
+        <v>46.0</v>
       </c>
       <c r="E2" t="n" s="0">
         <v>1.0</v>
@@ -189,10 +174,10 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>406.0246887207031</v>
+        <v>3.0859999656677246</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -206,7 +191,7 @@
         <v>15</v>
       </c>
       <c r="D3" t="n" s="0">
-        <v>1985.0</v>
+        <v>46.0</v>
       </c>
       <c r="E3" t="n" s="0">
         <v>1.0</v>
@@ -221,27 +206,27 @@
         <v>1</v>
       </c>
       <c r="I3" t="n" s="0">
-        <v>356.0078125</v>
+        <v>3.0450000762939453</v>
       </c>
       <c r="J3" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s" s="0">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n" s="0">
-        <v>1985.0</v>
+        <v>54.0</v>
       </c>
       <c r="E4" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F4" t="n" s="0">
         <v>1.0</v>
@@ -253,74 +238,10 @@
         <v>1</v>
       </c>
       <c r="I4" t="n" s="0">
-        <v>390.1156311035156</v>
+        <v>2.3299999237060547</v>
       </c>
       <c r="J4" t="b" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>20</v>
-      </c>
-      <c r="D5" t="n" s="0">
-        <v>1984.0</v>
-      </c>
-      <c r="E5" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="F5" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G5" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H5" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n" s="0">
-        <v>229.5042266845703</v>
-      </c>
-      <c r="J5" t="b" s="0">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="D6" t="n" s="0">
-        <v>1985.0</v>
-      </c>
-      <c r="E6" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="F6" t="n" s="0">
-        <v>6.0</v>
-      </c>
-      <c r="G6" t="b" s="0">
-        <v>0</v>
-      </c>
-      <c r="H6" t="b" s="0">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n" s="0">
-        <v>422.91876220703125</v>
-      </c>
-      <c r="J6" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
